--- a/pages/exoformule/formule.xlsx
+++ b/pages/exoformule/formule.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Cours\0- pédagogie\0 Paquetage scrom\SuperSite\pages\exoformule\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC668CF1-24D2-436A-B709-4FB752DE06E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B3C1332-8F3E-4A26-AD33-BD063796FEE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="1" activeTab="3" xr2:uid="{265E9A38-2995-4177-9081-96CEA6BA5440}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="13776" firstSheet="1" activeTab="3" xr2:uid="{265E9A38-2995-4177-9081-96CEA6BA5440}"/>
   </bookViews>
   <sheets>
     <sheet name="Mono" sheetId="1" r:id="rId1"/>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1642" uniqueCount="889">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1642" uniqueCount="890">
   <si>
     <t>VI</t>
   </si>
@@ -2720,6 +2720,9 @@
   </si>
   <si>
     <t>Loi d'Ohm \\(U=\\)</t>
+  </si>
+  <si>
+    <t>1Ah</t>
   </si>
 </sst>
 </file>
@@ -6936,7 +6939,7 @@
         <v>274</v>
       </c>
       <c r="D17" t="s">
-        <v>275</v>
+        <v>889</v>
       </c>
       <c r="E17" t="s">
         <v>276</v>
